--- a/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486486_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Primera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486486_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>G. KORSANTIA</t>
+          <t>O. HANZLIK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.0021</v>
+        <v>3.9665</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7265</v>
+        <v>3.5406</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2756</v>
+        <v>0.4259</v>
       </c>
       <c r="G2" t="n">
-        <v>-2.129</v>
+        <v>1.9746</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5325</v>
+        <v>1.4535</v>
       </c>
       <c r="I2" t="n">
-        <v>-2.6615</v>
+        <v>0.5212</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.6818</v>
+        <v>2.7867</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.8236</v>
+        <v>0.1642</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.8582</v>
+        <v>2.6225</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.4471</v>
+        <v>-0.8121</v>
       </c>
       <c r="N2" t="n">
-        <v>1.3562</v>
+        <v>1.2892</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.8033</v>
+        <v>-2.1013</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.6525</v>
+        <v>1.0875</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.3926</v>
+        <v>-0.2175</v>
       </c>
       <c r="R2" t="n">
-        <v>1.7401</v>
+        <v>1.305</v>
       </c>
       <c r="S2" t="n">
-        <v>4.8282</v>
+        <v>-0.2256</v>
       </c>
       <c r="T2" t="n">
-        <v>3.8455</v>
+        <v>-0.1586</v>
       </c>
       <c r="U2" t="n">
-        <v>0.9827</v>
+        <v>-0.067</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9554</v>
+        <v>1.13</v>
       </c>
       <c r="W2" t="n">
-        <v>0.9554</v>
+        <v>1.13</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. HANZLIK</t>
+          <t>M. MOTOS CABODEVILLA</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6216</v>
+        <v>0.3204</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5348</v>
+        <v>-0.299</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08690000000000001</v>
+        <v>0.6194</v>
       </c>
       <c r="G3" t="n">
-        <v>1.9746</v>
+        <v>-0.2152</v>
       </c>
       <c r="H3" t="n">
-        <v>1.4535</v>
+        <v>0.0182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5212</v>
+        <v>-0.2335</v>
       </c>
       <c r="J3" t="n">
-        <v>2.7867</v>
+        <v>-0.7268</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1642</v>
+        <v>0.0182</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6225</v>
+        <v>-0.7451</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.8121</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2892</v>
+        <v>0</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.1013</v>
+        <v>0.5116000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>1.0875</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.305</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.5705</v>
+        <v>0.5357</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.1644</v>
+        <v>0.4278</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4061</v>
+        <v>0.1078</v>
       </c>
       <c r="V3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. ANSORREGUI DEBA</t>
+          <t>G. KORSANTIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8891</v>
+        <v>0.2421</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7878</v>
+        <v>-1.6637</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1013</v>
+        <v>1.9058</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.3229</v>
+        <v>-2.129</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.5539</v>
+        <v>0.5325</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.769</v>
+        <v>-2.6615</v>
       </c>
       <c r="J4" t="n">
-        <v>-2.1826</v>
+        <v>-1.6818</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.0495</v>
+        <v>-0.8236</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.1331</v>
+        <v>-0.8582</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1403</v>
+        <v>-0.4471</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4956</v>
+        <v>1.3562</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6359</v>
+        <v>-1.8033</v>
       </c>
       <c r="P4" t="n">
-        <v>0.435</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-2.3926</v>
       </c>
       <c r="R4" t="n">
-        <v>0.435</v>
+        <v>1.7401</v>
       </c>
       <c r="S4" t="n">
-        <v>4.5165</v>
+        <v>2.0681</v>
       </c>
       <c r="T4" t="n">
-        <v>3.5799</v>
+        <v>1.4553</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9366</v>
+        <v>0.6128</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.7395</v>
+        <v>0.9554</v>
       </c>
       <c r="W4" t="n">
-        <v>0.3904</v>
+        <v>0.9554</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MOTOS CABODEVILLA</t>
+          <t>I. ARROYO VARELA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0726</v>
+        <v>0.1749</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3927</v>
+        <v>0.4925</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4653</v>
+        <v>-0.3176</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.2152</v>
+        <v>-0.3587</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0182</v>
+        <v>2.3051</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2335</v>
+        <v>-2.6639</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7268</v>
+        <v>1.0669</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0182</v>
+        <v>0.949</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.7451</v>
+        <v>0.118</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5116000000000001</v>
+        <v>-1.4257</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.3562</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5116000000000001</v>
+        <v>-2.7819</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.305</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.2175</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2878</v>
+        <v>-0.2064</v>
       </c>
       <c r="T5" t="n">
-        <v>0.3341</v>
+        <v>-0.3569</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0463</v>
+        <v>0.1505</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.5649999999999999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>I. ARROYO VARELA</t>
+          <t>M. ANSORREGUI DEBA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4648</v>
+        <v>-0.8139999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.178</v>
+        <v>-0.4222</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2868</v>
+        <v>-0.3919</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.3587</v>
+        <v>-2.3229</v>
       </c>
       <c r="H6" t="n">
-        <v>2.3051</v>
+        <v>-1.5539</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.6639</v>
+        <v>-0.769</v>
       </c>
       <c r="J6" t="n">
-        <v>1.0669</v>
+        <v>-2.1826</v>
       </c>
       <c r="K6" t="n">
-        <v>0.949</v>
+        <v>-2.0495</v>
       </c>
       <c r="L6" t="n">
-        <v>0.118</v>
+        <v>-0.1331</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.4257</v>
+        <v>-0.1403</v>
       </c>
       <c r="N6" t="n">
-        <v>1.3562</v>
+        <v>0.4956</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.7819</v>
+        <v>-0.6359</v>
       </c>
       <c r="P6" t="n">
-        <v>1.305</v>
+        <v>0.435</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2175</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5225</v>
+        <v>0.435</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8461</v>
+        <v>1.8134</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.0274</v>
+        <v>1.3699</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1813</v>
+        <v>0.4434</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-0.7395</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.3904</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5649999999999999</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.3068</v>
+        <v>-1.6055</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2764</v>
+        <v>0.3942</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0304</v>
+        <v>-1.9996</v>
       </c>
       <c r="G7" t="n">
         <v>0.8234</v>
@@ -1000,13 +1000,13 @@
         <v>1.0875</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0225</v>
+        <v>-0.3212</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7534999999999999</v>
+        <v>-0.0829</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2691</v>
+        <v>-0.2382</v>
       </c>
       <c r="V7" t="n">
         <v>-1.8902</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>T. MCGHIE</t>
+          <t>A. ZUBIZARRETA ARANBARRI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1601</v>
+        <v>-2.4626</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.0033</v>
+        <v>-2.6871</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1568</v>
+        <v>0.2246</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8536</v>
+        <v>-1.8803</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4835</v>
+        <v>0.4592</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.3371</v>
+        <v>-2.3396</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.3283</v>
+        <v>-2.305</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.5411</v>
+        <v>-0.0698</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2128</v>
+        <v>-2.2352</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.5252</v>
+        <v>0.4247</v>
       </c>
       <c r="N8" t="n">
-        <v>1.0247</v>
+        <v>0.5291</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5499</v>
+        <v>-0.1044</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.435</v>
+      </c>
+      <c r="Q8" t="n">
         <v>-1.0875</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-2.3926</v>
-      </c>
       <c r="R8" t="n">
-        <v>1.305</v>
+        <v>0.6525</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1062</v>
+        <v>1.178</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2824</v>
+        <v>0.7054</v>
       </c>
       <c r="U8" t="n">
-        <v>0.3886</v>
+        <v>0.4726</v>
       </c>
       <c r="V8" t="n">
         <v>-1.3252</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. ZUBIZARRETA ARANBARRI</t>
+          <t>T. MCGHIE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1111,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2277</v>
+        <v>-2.7448</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.6064</v>
+        <v>-2.7113</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3787</v>
+        <v>-0.0335</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.8803</v>
+        <v>-0.8536</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4592</v>
+        <v>0.4835</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.3396</v>
+        <v>-1.3371</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.305</v>
+        <v>-0.3283</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.0698</v>
+        <v>-0.5411</v>
       </c>
       <c r="L9" t="n">
-        <v>-2.2352</v>
+        <v>0.2128</v>
       </c>
       <c r="M9" t="n">
-        <v>0.4247</v>
+        <v>-0.5252</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5291</v>
+        <v>1.0247</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1044</v>
+        <v>-1.5499</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.435</v>
+        <v>-1.0875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.0875</v>
+        <v>-2.3926</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6525</v>
+        <v>1.305</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4128</v>
+        <v>0.5215</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2139</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.6267</v>
+        <v>0.5119</v>
       </c>
       <c r="V9" t="n">
         <v>-1.3252</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.048</v>
+        <v>-3.2974</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.2487</v>
+        <v>-3.6215</v>
       </c>
       <c r="F10" t="n">
-        <v>0.2008</v>
+        <v>0.3241</v>
       </c>
       <c r="G10" t="n">
         <v>-3.8682</v>
@@ -1234,13 +1234,13 @@
         <v>0.6525</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.8323</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6165</v>
+        <v>0.0108</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2158</v>
+        <v>-0.0925</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.318</v>
+        <v>-4.3379</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.8486</v>
+        <v>-4.0843</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.4694</v>
+        <v>-0.2536</v>
       </c>
       <c r="G11" t="n">
         <v>-1.8661</v>
@@ -1312,13 +1312,13 @@
         <v>1.0875</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2996</v>
+        <v>0.6805</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4879</v>
+        <v>0.2764</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1883</v>
+        <v>0.4041</v>
       </c>
       <c r="V11" t="n">
         <v>-2.0647</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.432</v>
+        <v>-6.7863</v>
       </c>
       <c r="E12" t="n">
-        <v>-7.5625</v>
+        <v>-6.9785</v>
       </c>
       <c r="F12" t="n">
-        <v>0.1306</v>
+        <v>0.1922</v>
       </c>
       <c r="G12" t="n">
         <v>-5.5673</v>
@@ -1390,13 +1390,13 @@
         <v>1.0875</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1577</v>
+        <v>0.8033</v>
       </c>
       <c r="T12" t="n">
-        <v>0.3257</v>
+        <v>0.9097</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.168</v>
+        <v>-0.1064</v>
       </c>
       <c r="V12" t="n">
         <v>-0.9347</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-18.372</v>
+        <v>-17.3446</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.0675</v>
+        <v>-18.0403</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6958000000000002</v>
+        <v>0.6957999999999996</v>
       </c>
       <c r="G13" t="n">
         <v>-16.2633</v>
@@ -1444,7 +1444,7 @@
         <v>-11.836</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.8518</v>
+        <v>-5.851800000000001</v>
       </c>
       <c r="L13" t="n">
         <v>-5.984299999999999</v>
@@ -1468,13 +1468,13 @@
         <v>10.8751</v>
       </c>
       <c r="S13" t="n">
-        <v>5.7382</v>
+        <v>6.765600000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>3.5392</v>
+        <v>4.5665</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1989</v>
+        <v>2.199</v>
       </c>
       <c r="V13" t="n">
         <v>-6.759100000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8374</v>
+        <v>6.1649</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1502</v>
+        <v>3.262</v>
       </c>
       <c r="F14" t="n">
-        <v>2.6872</v>
+        <v>2.903</v>
       </c>
       <c r="G14" t="n">
         <v>5.3994</v>
@@ -1546,13 +1546,13 @@
         <v>1.9576</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.6697</v>
+        <v>-0.3422</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1214</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5484</v>
+        <v>-0.3326</v>
       </c>
       <c r="V14" t="n">
         <v>1.3252</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4043</v>
+        <v>3.8881</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8988</v>
+        <v>2.1223</v>
       </c>
       <c r="F15" t="n">
-        <v>2.5055</v>
+        <v>1.7658</v>
       </c>
       <c r="G15" t="n">
         <v>0.9666</v>
@@ -1624,13 +1624,13 @@
         <v>0.87</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0414</v>
+        <v>-0.5576</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9589</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9176</v>
+        <v>0.1778</v>
       </c>
       <c r="V15" t="n">
         <v>2.609</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.6719</v>
+        <v>3.5138</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9805</v>
+        <v>1.4217</v>
       </c>
       <c r="F16" t="n">
-        <v>1.6914</v>
+        <v>2.0921</v>
       </c>
       <c r="G16" t="n">
         <v>2.2165</v>
@@ -1702,13 +1702,13 @@
         <v>0.87</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.7399</v>
+        <v>-0.898</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7487</v>
+        <v>0.1899</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.4886</v>
+        <v>-1.0879</v>
       </c>
       <c r="V16" t="n">
         <v>1.3252</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. ARMUS</t>
+          <t>M. KAMBA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5484</v>
+        <v>2.612</v>
       </c>
       <c r="E17" t="n">
-        <v>1.264</v>
+        <v>0.8502</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2844</v>
+        <v>1.7618</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.2945</v>
+        <v>0.2141</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7057</v>
+        <v>0.6811</v>
       </c>
       <c r="I17" t="n">
-        <v>0.4112</v>
+        <v>-0.467</v>
       </c>
       <c r="J17" t="n">
-        <v>0.06660000000000001</v>
+        <v>-0.1212</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8514</v>
+        <v>-0.1611</v>
       </c>
       <c r="L17" t="n">
-        <v>0.918</v>
+        <v>0.0399</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3611</v>
+        <v>0.3354</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1457</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="O17" t="n">
         <v>-0.5068</v>
       </c>
       <c r="P17" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7401</v>
+        <v>1.9576</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5172</v>
+        <v>-0.4945</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6117</v>
+        <v>-0.1586</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0945</v>
+        <v>-0.3359</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5857</v>
+        <v>0.9347</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5857</v>
+        <v>1.13</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1952</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.4493</v>
+        <v>2.4686</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4765</v>
+        <v>-0.3647</v>
       </c>
       <c r="F18" t="n">
-        <v>2.9258</v>
+        <v>2.8333</v>
       </c>
       <c r="G18" t="n">
         <v>3.3541</v>
@@ -1858,13 +1858,13 @@
         <v>0.6525</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.2093</v>
+        <v>-1.19</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6729000000000001</v>
+        <v>-0.5612</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.5363</v>
+        <v>-0.6288</v>
       </c>
       <c r="V18" t="n">
         <v>0.7395</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.2057</v>
+        <v>2.0862</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2486</v>
+        <v>-0.5839</v>
       </c>
       <c r="F19" t="n">
-        <v>2.4543</v>
+        <v>2.6701</v>
       </c>
       <c r="G19" t="n">
         <v>3.1271</v>
@@ -1936,13 +1936,13 @@
         <v>0.6525</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2912</v>
+        <v>-0.4107</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2091</v>
+        <v>-0.1262</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5003</v>
+        <v>-0.2845</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1952</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. KAMBA</t>
+          <t>M. ARMUS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>2.0687</v>
+        <v>1.8047</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7383999999999999</v>
+        <v>0.7052</v>
       </c>
       <c r="F20" t="n">
-        <v>1.3303</v>
+        <v>1.0995</v>
       </c>
       <c r="G20" t="n">
-        <v>0.2141</v>
+        <v>-0.2945</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6811</v>
+        <v>-0.7057</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.467</v>
+        <v>0.4112</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1212</v>
+        <v>0.06660000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1611</v>
+        <v>-0.8514</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0399</v>
+        <v>0.918</v>
       </c>
       <c r="M20" t="n">
-        <v>0.3354</v>
+        <v>-0.3611</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8421999999999999</v>
+        <v>0.1457</v>
       </c>
       <c r="O20" t="n">
         <v>-0.5068</v>
       </c>
       <c r="P20" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.9576</v>
+        <v>1.7401</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.0378</v>
+        <v>-0.2265</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2704</v>
+        <v>0.0529</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.7674</v>
+        <v>-0.2794</v>
       </c>
       <c r="V20" t="n">
-        <v>0.9347</v>
+        <v>0.5857</v>
       </c>
       <c r="W20" t="n">
-        <v>1.13</v>
+        <v>0.5857</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1952</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. LEVY</t>
+          <t>A. MUÑOZ BORCHERS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.8012</v>
+        <v>-0.7115</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.7753</v>
+        <v>-2.7647</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0259</v>
+        <v>2.0532</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.4757</v>
+        <v>1.3738</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.961</v>
+        <v>0.0271</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4853</v>
+        <v>1.3467</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.7068</v>
+        <v>-0.6245000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7451</v>
+        <v>-0.4166</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0382</v>
+        <v>-0.2079</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2311</v>
+        <v>1.9984</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.216</v>
+        <v>0.4437</v>
       </c>
       <c r="O21" t="n">
-        <v>0.447</v>
+        <v>1.5546</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.6525</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.1751</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.5225</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3254</v>
+        <v>-0.3028</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.06850000000000001</v>
+        <v>0.0349</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2569</v>
+        <v>-0.3377</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. MUÑOZ BORCHERS</t>
+          <t>G. LEVY</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.0237</v>
+        <v>-0.7395</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.3235</v>
+        <v>-0.7753</v>
       </c>
       <c r="F22" t="n">
-        <v>2.2998</v>
+        <v>0.0358</v>
       </c>
       <c r="G22" t="n">
-        <v>1.3738</v>
+        <v>-0.4757</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0271</v>
+        <v>-0.961</v>
       </c>
       <c r="I22" t="n">
-        <v>1.3467</v>
+        <v>0.4853</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.6245000000000001</v>
+        <v>-0.7068</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.4166</v>
+        <v>-0.7451</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2079</v>
+        <v>0.0382</v>
       </c>
       <c r="M22" t="n">
-        <v>1.9984</v>
+        <v>0.2311</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4437</v>
+        <v>-0.216</v>
       </c>
       <c r="O22" t="n">
-        <v>1.5546</v>
+        <v>0.447</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6525</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.1751</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.5225</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.615</v>
+        <v>-0.2638</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5239</v>
+        <v>-0.06850000000000001</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0911</v>
+        <v>-0.1953</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2939</v>
+        <v>-0.9162</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.7914</v>
+        <v>-2.5679</v>
       </c>
       <c r="F23" t="n">
-        <v>1.4975</v>
+        <v>1.6516</v>
       </c>
       <c r="G23" t="n">
         <v>0.7049</v>
@@ -2248,13 +2248,13 @@
         <v>1.5225</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8238</v>
+        <v>-0.4461</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.7413999999999999</v>
+        <v>-0.5179</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0823</v>
+        <v>0.0718</v>
       </c>
       <c r="V23" t="n">
         <v>0.5649999999999999</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.695</v>
+        <v>-1.7991</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.1123</v>
+        <v>-2.0006</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4173</v>
+        <v>0.2015</v>
       </c>
       <c r="G24" t="n">
         <v>-0.3231</v>
@@ -2326,13 +2326,13 @@
         <v>0.2175</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.502</v>
+        <v>-0.606</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.411</v>
+        <v>-0.2992</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.091</v>
+        <v>-0.3067</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>18.3719</v>
+        <v>18.372</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.6957000000000004</v>
+        <v>-0.6956999999999995</v>
       </c>
       <c r="F25" t="n">
-        <v>19.0676</v>
+        <v>19.0677</v>
       </c>
       <c r="G25" t="n">
         <v>16.2632</v>
@@ -2380,7 +2380,7 @@
         <v>4.4274</v>
       </c>
       <c r="K25" t="n">
-        <v>-9.259099999999998</v>
+        <v>-9.2591</v>
       </c>
       <c r="L25" t="n">
         <v>13.6864</v>
@@ -2389,10 +2389,10 @@
         <v>11.8361</v>
       </c>
       <c r="N25" t="n">
-        <v>5.851800000000001</v>
+        <v>5.8518</v>
       </c>
       <c r="O25" t="n">
-        <v>5.983999999999999</v>
+        <v>5.984</v>
       </c>
       <c r="P25" t="n">
         <v>1.0876</v>
@@ -2404,7 +2404,7 @@
         <v>11.9628</v>
       </c>
       <c r="S25" t="n">
-        <v>-5.738300000000001</v>
+        <v>-5.7382</v>
       </c>
       <c r="T25" t="n">
         <v>-2.1989</v>
